--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,10 +462,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1435740686591245</v>
+        <v>0.05119547972687255</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2825695601698431</v>
+        <v>0.1723810003095453</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.6245972084191397</v>
+        <v>0.3269606724357312</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.9115180612170624</v>
+        <v>0.4577566997286581</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.206592477061594</v>
+        <v>0.1248554013307271</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.7923842876232139</v>
+        <v>0.4648816105276414</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>41.53105640107143</v>
+        <v>37.12361785168907</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1653339199825712</v>
+        <v>0.04936285677125984</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2279587253590042</v>
+        <v>0.295722138628946</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-0.7765736986831552</v>
+        <v>0.2662824404374072</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.024531998427077</v>
+        <v>0.3906746742611053</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2100530619966359</v>
+        <v>0.1717263648669213</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8166694491279136</v>
+        <v>0.2996293665517934</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>43.19968262785282</v>
+        <v>26.83387623469105</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.02464051155673452</v>
+        <v>0.03783270826627794</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2149866719864041</v>
+        <v>0.2265455152274733</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.155509812787406</v>
+        <v>0.2179287458872879</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.2301429744024724</v>
+        <v>0.3063945625882369</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2024103302164808</v>
+        <v>0.227710563206857</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.126829869505083</v>
+        <v>0.173142922388468</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>52.25216210863693</v>
+        <v>64.40175761813362</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.0453085296461655</v>
+        <v>0.2195874629366987</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2276752083090965</v>
+        <v>0.2568589042273156</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.2505402629884826</v>
+        <v>0.874639603520473</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.364103325745524</v>
+        <v>1.301714781710927</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1616418482764186</v>
+        <v>0.1226797408856356</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.2921540737209244</v>
+        <v>1.871807725297752</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>56.87534776321954</v>
+        <v>69.73187805769746</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3095587294581625</v>
+        <v>0.2539668750519277</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2464448250390205</v>
+        <v>0.2630822260452915</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.198302151452765</v>
+        <v>0.9681787304923422</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.708390110944873</v>
+        <v>1.333167686194503</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.148235001119072</v>
+        <v>0.1736478975081723</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.176981386058525</v>
+        <v>1.523322255290393</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>59.64014299681945</v>
+        <v>70.21898814015647</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.633508755882181</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3743474569087623</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2.526188536404583</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>4.084136097091443</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1172055785578786</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>12.23768193902375</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>41.90568067994335</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>